--- a/runs/RELX/2026-10-14/bear/scratch/b_growth_3/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_growth_3/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1872.386509407173</v>
+        <v>1925.451639641748</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600960394000001</v>
+        <v>0.089224054516</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10641.28614753486</v>
+        <v>10799.8846193864</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>35075.66027695208</v>
+        <v>38513.88168788778</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>23218.8783578204</v>
+        <v>26217.40994948584</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>33860.16450535526</v>
+        <v>37017.29456887224</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>26863.16450535526</v>
+        <v>30020.29456887224</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>25737.77817858382</v>
+        <v>28967.96272017942</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>14.75997614805825</v>
+        <v>16.61240670585401</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1475.997614805825</v>
+        <v>1661.240670585401</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4673411711</v>
+        <v>-0.4004905555</v>
       </c>
     </row>
   </sheetData>
